--- a/doc/convolution sizes.xlsx
+++ b/doc/convolution sizes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushn\Dropbox\software\projects\cv\local\cv-workbench\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushn\Dropbox\software\projects\cv\cv-workbench\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11192B8A-C3DF-44DB-8872-E81DC5A461E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0C7E79-87BC-4F7F-AFEB-068DDB1685C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{361771D6-7B40-4CB9-9BC1-EB8C3A2D2A49}"/>
+    <workbookView xWindow="-28545" yWindow="2535" windowWidth="25620" windowHeight="11070" xr2:uid="{361771D6-7B40-4CB9-9BC1-EB8C3A2D2A49}"/>
   </bookViews>
   <sheets>
     <sheet name="convolution sizes" sheetId="1" r:id="rId1"/>
@@ -28,11 +28,27 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>input image</t>
+  </si>
+  <si>
+    <t>kernel</t>
+  </si>
+  <si>
+    <t>output image</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -66,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -75,7 +91,108 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -87,10 +204,49 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -99,7 +255,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -112,179 +311,51 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="thick">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thick">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -307,15 +378,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -330,8 +401,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="971550" y="596900"/>
-          <a:ext cx="19050" cy="1860550"/>
+          <a:off x="990600" y="914400"/>
+          <a:ext cx="0" cy="1520190"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -361,13 +432,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>406400</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>311150</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -426,15 +497,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:colOff>601345</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>16510</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -449,8 +520,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="2432050" y="3009900"/>
-          <a:ext cx="4260850" cy="6350"/>
+          <a:off x="2430145" y="2981325"/>
+          <a:ext cx="4827905" cy="6985"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -480,13 +551,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>317500</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -546,13 +617,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -599,13 +670,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>184150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -671,13 +742,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>260350</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -737,13 +808,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>539750</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -790,13 +861,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -843,13 +914,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>234950</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>234950</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -896,13 +967,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>82550</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -967,13 +1038,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1334,153 +1405,176 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C981200-E8AD-49D9-AC2C-9FFCF7D04B62}">
-  <dimension ref="D4:L14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:L16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13"/>
     </row>
-    <row r="5" spans="4:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E5" s="6">
+    <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E7" s="3">
         <v>0</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F7" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G7" s="3">
         <v>2</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H7" s="3">
         <v>3</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I7" s="3">
         <v>4</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J7" s="3">
         <v>5</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K7" s="3">
         <v>6</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L7" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="4:12" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="D6">
+    <row r="8" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="D8">
         <v>0</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
     </row>
-    <row r="7" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D7">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="2"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="11"/>
     </row>
-    <row r="8" spans="4:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D8">
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D10">
         <v>2</v>
       </c>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="2"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="11"/>
     </row>
-    <row r="9" spans="4:12" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="D9">
+    <row r="11" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="D11">
         <v>3</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="2"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="11"/>
     </row>
-    <row r="10" spans="4:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D10">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12">
         <v>4</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="2"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="11"/>
     </row>
-    <row r="11" spans="4:12" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="D11">
+    <row r="13" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="D13">
         <v>5</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="2"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="11"/>
     </row>
-    <row r="12" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D14">
         <v>6</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="2"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="11"/>
     </row>
-    <row r="13" spans="4:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D13">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D15">
         <v>7</v>
       </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
     </row>
-    <row r="14" spans="4:12" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="86" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>